--- a/Bases_de_Dados/FootyStats/Portugal Liga NOS_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Portugal Liga NOS_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP211"/>
+  <dimension ref="A1:BP213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.42</v>
@@ -1786,7 +1786,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ12" t="n">
         <v>0.92</v>
@@ -3966,7 +3966,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>3</v>
       </c>
       <c r="AP20" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ20" t="n">
         <v>2.5</v>
@@ -6146,7 +6146,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR26" t="n">
         <v>1.22</v>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ29" t="n">
         <v>0.92</v>
@@ -8108,7 +8108,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR35" t="n">
         <v>2.1</v>
@@ -10724,7 +10724,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR47" t="n">
         <v>1.44</v>
@@ -10939,7 +10939,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.92</v>
@@ -11375,10 +11375,10 @@
         <v>2</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR50" t="n">
         <v>1.48</v>
@@ -14863,7 +14863,7 @@
         <v>1</v>
       </c>
       <c r="AP66" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ66" t="n">
         <v>1.17</v>
@@ -15302,7 +15302,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ68" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR68" t="n">
         <v>1.07</v>
@@ -15517,7 +15517,7 @@
         <v>1.33</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ69" t="n">
         <v>0.64</v>
@@ -16174,7 +16174,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR72" t="n">
         <v>2.42</v>
@@ -18572,7 +18572,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR83" t="n">
         <v>2.13</v>
@@ -18787,7 +18787,7 @@
         <v>2</v>
       </c>
       <c r="AP84" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ84" t="n">
         <v>1.36</v>
@@ -19441,7 +19441,7 @@
         <v>2.5</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ87" t="n">
         <v>2.45</v>
@@ -20098,7 +20098,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR90" t="n">
         <v>1.7</v>
@@ -22493,7 +22493,7 @@
         <v>0.2</v>
       </c>
       <c r="AP101" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ101" t="n">
         <v>0.18</v>
@@ -22932,7 +22932,7 @@
         <v>1</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR103" t="n">
         <v>1.12</v>
@@ -23147,7 +23147,7 @@
         <v>2.6</v>
       </c>
       <c r="AP104" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ104" t="n">
         <v>2.45</v>
@@ -24240,7 +24240,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR109" t="n">
         <v>1.16</v>
@@ -25112,7 +25112,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR113" t="n">
         <v>1.4</v>
@@ -26199,7 +26199,7 @@
         <v>1.83</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ118" t="n">
         <v>1.42</v>
@@ -27510,7 +27510,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ124" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR124" t="n">
         <v>1.16</v>
@@ -27725,7 +27725,7 @@
         <v>1</v>
       </c>
       <c r="AP125" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ125" t="n">
         <v>0.92</v>
@@ -28382,7 +28382,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR128" t="n">
         <v>1.39</v>
@@ -30123,7 +30123,7 @@
         <v>2.71</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ136" t="n">
         <v>2.5</v>
@@ -30562,7 +30562,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ138" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR138" t="n">
         <v>1.42</v>
@@ -32085,7 +32085,7 @@
         <v>1.25</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ145" t="n">
         <v>0.83</v>
@@ -32742,7 +32742,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR148" t="n">
         <v>1.51</v>
@@ -33829,7 +33829,7 @@
         <v>0.71</v>
       </c>
       <c r="AP153" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ153" t="n">
         <v>0.64</v>
@@ -35576,7 +35576,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR161" t="n">
         <v>1.31</v>
@@ -35791,7 +35791,7 @@
         <v>3</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ162" t="n">
         <v>2.75</v>
@@ -37099,7 +37099,7 @@
         <v>1.22</v>
       </c>
       <c r="AP168" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ168" t="n">
         <v>0.92</v>
@@ -37756,7 +37756,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ171" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR171" t="n">
         <v>1.43</v>
@@ -38189,7 +38189,7 @@
         <v>1.1</v>
       </c>
       <c r="AP173" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ173" t="n">
         <v>1.17</v>
@@ -39718,7 +39718,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR180" t="n">
         <v>1.23</v>
@@ -41023,7 +41023,7 @@
         <v>1</v>
       </c>
       <c r="AP186" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ186" t="n">
         <v>0.92</v>
@@ -41462,7 +41462,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ188" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR188" t="n">
         <v>1.94</v>
@@ -42334,7 +42334,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ192" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR192" t="n">
         <v>1.2</v>
@@ -42767,7 +42767,7 @@
         <v>1</v>
       </c>
       <c r="AP194" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ194" t="n">
         <v>0.92</v>
@@ -42988,7 +42988,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ195" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR195" t="n">
         <v>1.68</v>
@@ -43203,7 +43203,7 @@
         <v>2.73</v>
       </c>
       <c r="AP196" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ196" t="n">
         <v>2.75</v>
@@ -46552,6 +46552,442 @@
       </c>
       <c r="BP211" t="n">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="n">
+        <v>8227434</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="n">
+        <v>46081.625</v>
+      </c>
+      <c r="F212" t="n">
+        <v>24</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>CD Nacional</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Sporting Braga</t>
+        </is>
+      </c>
+      <c r="I212" t="n">
+        <v>0</v>
+      </c>
+      <c r="J212" t="n">
+        <v>1</v>
+      </c>
+      <c r="K212" t="n">
+        <v>1</v>
+      </c>
+      <c r="L212" t="n">
+        <v>1</v>
+      </c>
+      <c r="M212" t="n">
+        <v>2</v>
+      </c>
+      <c r="N212" t="n">
+        <v>3</v>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>['59']</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>['11', '90+6']</t>
+        </is>
+      </c>
+      <c r="Q212" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="R212" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S212" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T212" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U212" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="V212" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W212" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X212" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y212" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z212" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA212" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB212" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC212" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD212" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE212" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF212" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG212" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH212" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AI212" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ212" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK212" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM212" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN212" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO212" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AP212" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AQ212" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AR212" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AS212" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AT212" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AU212" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV212" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW212" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX212" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY212" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ212" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA212" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB212" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC212" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD212" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE212" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF212" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BG212" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH212" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BI212" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BJ212" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BK212" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BL212" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BM212" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BN212" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BO212" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP212" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="n">
+        <v>8227432</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="n">
+        <v>46081.72916666666</v>
+      </c>
+      <c r="F213" t="n">
+        <v>24</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Vitória Guimarães</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="I213" t="n">
+        <v>0</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" t="n">
+        <v>0</v>
+      </c>
+      <c r="L213" t="n">
+        <v>1</v>
+      </c>
+      <c r="M213" t="n">
+        <v>1</v>
+      </c>
+      <c r="N213" t="n">
+        <v>2</v>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>['46']</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="Q213" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="R213" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="S213" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T213" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U213" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V213" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="W213" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X213" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="Y213" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z213" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA213" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB213" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC213" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD213" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE213" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF213" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AG213" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH213" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI213" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ213" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK213" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM213" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AN213" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO213" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AP213" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ213" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AR213" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS213" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AT213" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AU213" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV213" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW213" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX213" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY213" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ213" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA213" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB213" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC213" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD213" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BE213" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF213" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BG213" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH213" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="BI213" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BJ213" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BK213" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BL213" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BM213" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BN213" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BO213" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BP213" t="n">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Portugal Liga NOS_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Portugal Liga NOS_20252026.xlsx
@@ -46494,13 +46494,13 @@
         <v>6</v>
       </c>
       <c r="AW211" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX211" t="n">
         <v>10</v>
       </c>
       <c r="AY211" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ211" t="n">
         <v>16</v>

--- a/Bases_de_Dados/FootyStats/Portugal Liga NOS_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Portugal Liga NOS_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP213"/>
+  <dimension ref="A1:BP217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1568,7 +1568,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ13" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ14" t="n">
         <v>0.83</v>
@@ -3748,7 +3748,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ18" t="n">
         <v>2.75</v>
@@ -6361,10 +6361,10 @@
         <v>3</v>
       </c>
       <c r="AP27" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR27" t="n">
         <v>1.32</v>
@@ -7018,7 +7018,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR30" t="n">
         <v>1.02</v>
@@ -7451,7 +7451,7 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ32" t="n">
         <v>0.92</v>
@@ -7672,7 +7672,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR33" t="n">
         <v>1.4</v>
@@ -8105,7 +8105,7 @@
         <v>3</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ35" t="n">
         <v>1.69</v>
@@ -8326,7 +8326,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR36" t="n">
         <v>1.07</v>
@@ -8762,7 +8762,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR38" t="n">
         <v>2.61</v>
@@ -10503,7 +10503,7 @@
         <v>3</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ46" t="n">
         <v>2.75</v>
@@ -11160,7 +11160,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ49" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR49" t="n">
         <v>1.18</v>
@@ -11593,7 +11593,7 @@
         <v>1</v>
       </c>
       <c r="AP51" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ51" t="n">
         <v>0.92</v>
@@ -11811,7 +11811,7 @@
         <v>0.5</v>
       </c>
       <c r="AP52" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ52" t="n">
         <v>0.92</v>
@@ -12032,7 +12032,7 @@
         <v>1</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR53" t="n">
         <v>0.97</v>
@@ -12250,7 +12250,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR54" t="n">
         <v>2.06</v>
@@ -14866,7 +14866,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR66" t="n">
         <v>1.22</v>
@@ -15081,7 +15081,7 @@
         <v>1</v>
       </c>
       <c r="AP67" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ67" t="n">
         <v>0.92</v>
@@ -15520,7 +15520,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR69" t="n">
         <v>1.36</v>
@@ -15738,7 +15738,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR70" t="n">
         <v>1.22</v>
@@ -15953,7 +15953,7 @@
         <v>0.75</v>
       </c>
       <c r="AP71" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ71" t="n">
         <v>0.92</v>
@@ -16392,7 +16392,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ73" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR73" t="n">
         <v>1.93</v>
@@ -17915,7 +17915,7 @@
         <v>3</v>
       </c>
       <c r="AP80" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ80" t="n">
         <v>2.5</v>
@@ -18790,7 +18790,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR84" t="n">
         <v>1.39</v>
@@ -19223,7 +19223,7 @@
         <v>0.5</v>
       </c>
       <c r="AP86" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ86" t="n">
         <v>0.92</v>
@@ -19444,7 +19444,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ87" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR87" t="n">
         <v>1.46</v>
@@ -19880,7 +19880,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR89" t="n">
         <v>1.14</v>
@@ -20313,10 +20313,10 @@
         <v>1</v>
       </c>
       <c r="AP91" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ91" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR91" t="n">
         <v>1.55</v>
@@ -20967,7 +20967,7 @@
         <v>0.6</v>
       </c>
       <c r="AP94" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ94" t="n">
         <v>0.91</v>
@@ -22060,7 +22060,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR99" t="n">
         <v>1.61</v>
@@ -22714,7 +22714,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR102" t="n">
         <v>1.24</v>
@@ -23150,7 +23150,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ104" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR104" t="n">
         <v>1.32</v>
@@ -23365,7 +23365,7 @@
         <v>0.67</v>
       </c>
       <c r="AP105" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ105" t="n">
         <v>0.92</v>
@@ -23583,10 +23583,10 @@
         <v>0.8</v>
       </c>
       <c r="AP106" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR106" t="n">
         <v>1.04</v>
@@ -25330,7 +25330,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR114" t="n">
         <v>1.43</v>
@@ -25981,7 +25981,7 @@
         <v>3</v>
       </c>
       <c r="AP117" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ117" t="n">
         <v>2.75</v>
@@ -26635,7 +26635,7 @@
         <v>1</v>
       </c>
       <c r="AP120" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ120" t="n">
         <v>0.91</v>
@@ -27292,7 +27292,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ123" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR123" t="n">
         <v>1.25</v>
@@ -27946,7 +27946,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ126" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR126" t="n">
         <v>1.55</v>
@@ -28597,7 +28597,7 @@
         <v>1.43</v>
       </c>
       <c r="AP129" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ129" t="n">
         <v>0.92</v>
@@ -28818,7 +28818,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR130" t="n">
         <v>1.55</v>
@@ -29251,7 +29251,7 @@
         <v>1</v>
       </c>
       <c r="AP132" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ132" t="n">
         <v>0.92</v>
@@ -29908,7 +29908,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR135" t="n">
         <v>2.02</v>
@@ -31216,7 +31216,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ141" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR141" t="n">
         <v>1.47</v>
@@ -31867,7 +31867,7 @@
         <v>2.75</v>
       </c>
       <c r="AP144" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ144" t="n">
         <v>2.5</v>
@@ -32303,7 +32303,7 @@
         <v>0.71</v>
       </c>
       <c r="AP146" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ146" t="n">
         <v>0.92</v>
@@ -32960,7 +32960,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ149" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR149" t="n">
         <v>1.25</v>
@@ -33175,7 +33175,7 @@
         <v>1.25</v>
       </c>
       <c r="AP150" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ150" t="n">
         <v>0.92</v>
@@ -33614,7 +33614,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR152" t="n">
         <v>1.28</v>
@@ -33832,7 +33832,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ153" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR153" t="n">
         <v>1.19</v>
@@ -34483,7 +34483,7 @@
         <v>1.11</v>
       </c>
       <c r="AP156" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ156" t="n">
         <v>0.83</v>
@@ -34922,7 +34922,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR158" t="n">
         <v>1.27</v>
@@ -35137,10 +35137,10 @@
         <v>2.5</v>
       </c>
       <c r="AP159" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ159" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR159" t="n">
         <v>1.09</v>
@@ -35358,7 +35358,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR160" t="n">
         <v>1.31</v>
@@ -35573,7 +35573,7 @@
         <v>1.44</v>
       </c>
       <c r="AP161" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ161" t="n">
         <v>1.69</v>
@@ -36448,7 +36448,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ165" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR165" t="n">
         <v>1.15</v>
@@ -38192,7 +38192,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR173" t="n">
         <v>1.41</v>
@@ -38625,7 +38625,7 @@
         <v>0.89</v>
       </c>
       <c r="AP175" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ175" t="n">
         <v>0.92</v>
@@ -39061,10 +39061,10 @@
         <v>1.67</v>
       </c>
       <c r="AP177" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR177" t="n">
         <v>1.66</v>
@@ -39497,10 +39497,10 @@
         <v>2.56</v>
       </c>
       <c r="AP179" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ179" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR179" t="n">
         <v>1.26</v>
@@ -40372,7 +40372,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ183" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR183" t="n">
         <v>1.39</v>
@@ -42116,7 +42116,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ191" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR191" t="n">
         <v>1.32</v>
@@ -42331,7 +42331,7 @@
         <v>0.7</v>
       </c>
       <c r="AP192" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ192" t="n">
         <v>0.75</v>
@@ -42985,7 +42985,7 @@
         <v>1.73</v>
       </c>
       <c r="AP195" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ195" t="n">
         <v>1.69</v>
@@ -43642,7 +43642,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ198" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR198" t="n">
         <v>2.28</v>
@@ -43857,10 +43857,10 @@
         <v>1</v>
       </c>
       <c r="AP199" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AQ199" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR199" t="n">
         <v>1.01</v>
@@ -44514,7 +44514,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ202" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR202" t="n">
         <v>1.28</v>
@@ -46988,6 +46988,878 @@
       </c>
       <c r="BP213" t="n">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="n">
+        <v>8227433</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="n">
+        <v>46082.52083333334</v>
+      </c>
+      <c r="F214" t="n">
+        <v>24</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>CD Tondela</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Santa Clara</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>1</v>
+      </c>
+      <c r="J214" t="n">
+        <v>1</v>
+      </c>
+      <c r="K214" t="n">
+        <v>2</v>
+      </c>
+      <c r="L214" t="n">
+        <v>2</v>
+      </c>
+      <c r="M214" t="n">
+        <v>2</v>
+      </c>
+      <c r="N214" t="n">
+        <v>4</v>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>['10', '60']</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>['15', '88']</t>
+        </is>
+      </c>
+      <c r="Q214" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R214" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S214" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="T214" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U214" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="V214" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W214" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X214" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z214" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AA214" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB214" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC214" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD214" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF214" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG214" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AH214" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI214" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ214" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK214" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AL214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM214" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN214" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AO214" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AP214" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AQ214" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AR214" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AS214" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT214" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU214" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV214" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW214" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX214" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY214" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ214" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA214" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB214" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC214" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD214" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BE214" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF214" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BG214" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH214" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BI214" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BJ214" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BK214" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BL214" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BM214" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BN214" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BO214" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="BP214" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="n">
+        <v>8227344</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="n">
+        <v>46082.625</v>
+      </c>
+      <c r="F215" t="n">
+        <v>24</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Casa Pia</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Moreirense FC</t>
+        </is>
+      </c>
+      <c r="I215" t="n">
+        <v>1</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" t="n">
+        <v>1</v>
+      </c>
+      <c r="L215" t="n">
+        <v>1</v>
+      </c>
+      <c r="M215" t="n">
+        <v>1</v>
+      </c>
+      <c r="N215" t="n">
+        <v>2</v>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>['40']</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>['62']</t>
+        </is>
+      </c>
+      <c r="Q215" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R215" t="n">
+        <v>2</v>
+      </c>
+      <c r="S215" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T215" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U215" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="V215" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W215" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X215" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z215" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA215" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB215" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AC215" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD215" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="AE215" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF215" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AG215" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AH215" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI215" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AJ215" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK215" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM215" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO215" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ215" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR215" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AS215" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AT215" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AU215" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV215" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW215" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX215" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY215" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ215" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA215" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB215" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC215" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD215" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BE215" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="BF215" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BG215" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BH215" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BI215" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BJ215" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BK215" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BL215" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BM215" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BN215" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BO215" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP215" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="n">
+        <v>8227345</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="n">
+        <v>46082.72916666666</v>
+      </c>
+      <c r="F216" t="n">
+        <v>24</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Rio Ave FC</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="I216" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" t="n">
+        <v>0</v>
+      </c>
+      <c r="L216" t="n">
+        <v>0</v>
+      </c>
+      <c r="M216" t="n">
+        <v>0</v>
+      </c>
+      <c r="N216" t="n">
+        <v>0</v>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q216" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="R216" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="S216" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T216" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U216" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="V216" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="W216" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X216" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z216" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="AA216" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AB216" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC216" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD216" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE216" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF216" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG216" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH216" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI216" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ216" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AK216" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM216" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN216" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AO216" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AP216" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AQ216" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR216" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AS216" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT216" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AU216" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV216" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW216" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX216" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY216" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ216" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA216" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB216" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC216" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD216" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BE216" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF216" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BG216" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH216" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI216" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BJ216" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BK216" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BL216" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM216" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BN216" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO216" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BP216" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="n">
+        <v>8227301</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="n">
+        <v>46083.71875</v>
+      </c>
+      <c r="F217" t="n">
+        <v>24</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Gil Vicente</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Benfica</t>
+        </is>
+      </c>
+      <c r="I217" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" t="n">
+        <v>1</v>
+      </c>
+      <c r="K217" t="n">
+        <v>1</v>
+      </c>
+      <c r="L217" t="n">
+        <v>1</v>
+      </c>
+      <c r="M217" t="n">
+        <v>2</v>
+      </c>
+      <c r="N217" t="n">
+        <v>3</v>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>['35', '73']</t>
+        </is>
+      </c>
+      <c r="Q217" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="R217" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S217" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T217" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U217" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="V217" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="W217" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X217" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Y217" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z217" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA217" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB217" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC217" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD217" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE217" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF217" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG217" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH217" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI217" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AJ217" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AK217" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AL217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM217" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AN217" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AO217" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AP217" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ217" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AR217" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS217" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AT217" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AU217" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV217" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW217" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX217" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY217" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ217" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA217" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB217" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC217" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD217" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE217" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF217" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BG217" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH217" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI217" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ217" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BK217" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BL217" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM217" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BN217" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BO217" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BP217" t="n">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Portugal Liga NOS_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Portugal Liga NOS_20252026.xlsx
@@ -3613,7 +3613,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>8227337</v>
+        <v>8227335</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -3633,31 +3633,31 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -3666,89 +3666,89 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>['8']</t>
+          <t>['11', '14', '36']</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>2.65</v>
+        <v>5.03</v>
       </c>
       <c r="R15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI15" t="n">
         <v>1.83</v>
       </c>
-      <c r="S15" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V15" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X15" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF15" t="n">
+      <c r="AJ15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK15" t="n">
         <v>2.2</v>
       </c>
-      <c r="AG15" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AJ15" t="n">
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
         <v>1.5</v>
       </c>
-      <c r="AK15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0.92</v>
-      </c>
       <c r="AQ15" t="n">
-        <v>1.15</v>
+        <v>1.69</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3763,67 +3763,67 @@
         <v>3</v>
       </c>
       <c r="AV15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AW15" t="n">
         <v>9</v>
       </c>
       <c r="AX15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY15" t="n">
         <v>12</v>
       </c>
       <c r="AZ15" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB15" t="n">
         <v>5</v>
       </c>
-      <c r="BA15" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>0</v>
-      </c>
       <c r="BC15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.47</v>
+        <v>3.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.76</v>
+        <v>9.57</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.52</v>
+        <v>1.36</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.48</v>
+        <v>3.48</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="BL15" t="n">
-        <v>1.49</v>
+        <v>1.9</v>
       </c>
       <c r="BM15" t="n">
-        <v>3.2</v>
+        <v>2.28</v>
       </c>
       <c r="BN15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP15" t="n">
         <v>1.26</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>1.12</v>
       </c>
     </row>
     <row r="16">
@@ -3831,7 +3831,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>8227335</v>
+        <v>8227337</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -3851,31 +3851,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -3884,77 +3884,77 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>['11', '14', '36']</t>
+          <t>['8']</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>5.03</v>
+        <v>2.65</v>
       </c>
       <c r="R16" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="S16" t="n">
-        <v>2.23</v>
+        <v>4.75</v>
       </c>
       <c r="T16" t="n">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="U16" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="V16" t="n">
-        <v>2.7</v>
+        <v>4.26</v>
       </c>
       <c r="W16" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="X16" t="n">
-        <v>6.5</v>
+        <v>12</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.4</v>
+        <v>1.91</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.55</v>
+        <v>4.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AD16" t="n">
-        <v>9.5</v>
+        <v>6.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>3.34</v>
+        <v>2.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>2</v>
+        <v>2.83</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.2</v>
+        <v>1.13</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="AN16" t="n">
         <v>0</v>
@@ -3963,10 +3963,10 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.5</v>
+        <v>0.92</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.69</v>
+        <v>1.15</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -3981,67 +3981,67 @@
         <v>3</v>
       </c>
       <c r="AV16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AW16" t="n">
         <v>9</v>
       </c>
       <c r="AX16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY16" t="n">
         <v>12</v>
       </c>
       <c r="AZ16" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="BA16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BB16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BD16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BM16" t="n">
         <v>3.2</v>
       </c>
-      <c r="BE16" t="n">
-        <v>9.57</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>2.28</v>
-      </c>
       <c r="BN16" t="n">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="BP16" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="17">
@@ -7755,7 +7755,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>8227336</v>
+        <v>8227231</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -7775,197 +7775,197 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14', '24']</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22', '88']</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>2.74</v>
+        <v>4.6</v>
       </c>
       <c r="R34" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>2.49</v>
       </c>
       <c r="T34" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="U34" t="n">
-        <v>2.45</v>
+        <v>2.84</v>
       </c>
       <c r="V34" t="n">
-        <v>3.55</v>
+        <v>2.7</v>
       </c>
       <c r="W34" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="X34" t="n">
-        <v>9</v>
+        <v>6.65</v>
       </c>
       <c r="Y34" t="n">
         <v>1.05</v>
       </c>
       <c r="Z34" t="n">
-        <v>2</v>
+        <v>4.36</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="AB34" t="n">
-        <v>3.96</v>
+        <v>1.81</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AD34" t="n">
-        <v>6.15</v>
+        <v>10</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.55</v>
+        <v>1.97</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="AI34" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AR34" t="n">
         <v>2.1</v>
       </c>
-      <c r="AJ34" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AS34" t="n">
-        <v>1.12</v>
+        <v>1.54</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.49</v>
+        <v>3.64</v>
       </c>
       <c r="AU34" t="n">
         <v>3</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW34" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AX34" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AY34" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AZ34" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="BA34" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BC34" t="n">
         <v>8</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.57</v>
+        <v>3.78</v>
       </c>
       <c r="BE34" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="BF34" t="n">
-        <v>3.7</v>
+        <v>1.38</v>
       </c>
       <c r="BG34" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BI34" t="n">
         <v>1.45</v>
       </c>
-      <c r="BH34" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="BI34" t="n">
-        <v>1.52</v>
-      </c>
       <c r="BJ34" t="n">
-        <v>1.98</v>
+        <v>2.48</v>
       </c>
       <c r="BK34" t="n">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="BL34" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="BM34" t="n">
-        <v>2.87</v>
+        <v>2.29</v>
       </c>
       <c r="BN34" t="n">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="BO34" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="BP34" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="35">
@@ -7973,7 +7973,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>8227231</v>
+        <v>8227336</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -7993,197 +7993,197 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>['14', '24']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>['22', '88']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>4.6</v>
+        <v>2.74</v>
       </c>
       <c r="R35" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="S35" t="n">
-        <v>2.49</v>
+        <v>5</v>
       </c>
       <c r="T35" t="n">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="U35" t="n">
-        <v>2.84</v>
+        <v>2.45</v>
       </c>
       <c r="V35" t="n">
-        <v>2.7</v>
+        <v>3.55</v>
       </c>
       <c r="W35" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="X35" t="n">
-        <v>6.65</v>
+        <v>9</v>
       </c>
       <c r="Y35" t="n">
         <v>1.05</v>
       </c>
       <c r="Z35" t="n">
-        <v>4.36</v>
+        <v>2</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.81</v>
+        <v>3.96</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AD35" t="n">
-        <v>10</v>
+        <v>6.15</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AF35" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.97</v>
+        <v>2.55</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.93</v>
+        <v>1.44</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AJ35" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="AN35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.69</v>
+        <v>0.92</v>
       </c>
       <c r="AR35" t="n">
-        <v>2.1</v>
+        <v>1.37</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.54</v>
+        <v>1.12</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.64</v>
+        <v>2.49</v>
       </c>
       <c r="AU35" t="n">
         <v>3</v>
       </c>
       <c r="AV35" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AX35" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AY35" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AZ35" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="BA35" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BB35" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
         <v>8</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.78</v>
+        <v>1.57</v>
       </c>
       <c r="BE35" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.38</v>
+        <v>3.7</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="BH35" t="n">
-        <v>3.32</v>
+        <v>2.55</v>
       </c>
       <c r="BI35" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="BJ35" t="n">
-        <v>2.48</v>
+        <v>1.98</v>
       </c>
       <c r="BK35" t="n">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="BL35" t="n">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="BM35" t="n">
-        <v>2.29</v>
+        <v>2.87</v>
       </c>
       <c r="BN35" t="n">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="BO35" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="BP35" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="36">
@@ -10589,7 +10589,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>8227366</v>
+        <v>8227210</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -10609,113 +10609,113 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N47" t="n">
         <v>3</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>['9', '90+7']</t>
+          <t>['66']</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>['19']</t>
+          <t>['74', '89']</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>2.3</v>
+        <v>3.17</v>
       </c>
       <c r="R47" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="S47" t="n">
-        <v>6.05</v>
+        <v>3.94</v>
       </c>
       <c r="T47" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="U47" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="V47" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="W47" t="n">
         <v>1.3</v>
       </c>
       <c r="X47" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="Y47" t="n">
         <v>1.05</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.65</v>
+        <v>2.27</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="AB47" t="n">
-        <v>5.05</v>
+        <v>2.72</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AD47" t="n">
-        <v>6.6</v>
+        <v>6.95</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.49</v>
+        <v>2.29</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="AI47" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.97</v>
+        <v>1.6</v>
       </c>
       <c r="AN47" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AO47" t="n">
         <v>0.5</v>
@@ -10724,16 +10724,16 @@
         <v>0.92</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.44</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="AT47" t="n">
-        <v>2.23</v>
+        <v>1.72</v>
       </c>
       <c r="AU47" t="n">
         <v>6</v>
@@ -10742,64 +10742,64 @@
         <v>3</v>
       </c>
       <c r="AW47" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC47" t="n">
         <v>8</v>
       </c>
-      <c r="AX47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ47" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA47" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC47" t="n">
-        <v>7</v>
-      </c>
       <c r="BD47" t="n">
-        <v>1.31</v>
+        <v>1.7</v>
       </c>
       <c r="BE47" t="n">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="BF47" t="n">
-        <v>4.33</v>
+        <v>2.38</v>
       </c>
       <c r="BG47" t="n">
-        <v>1.54</v>
+        <v>1.26</v>
       </c>
       <c r="BH47" t="n">
-        <v>2.42</v>
+        <v>3.76</v>
       </c>
       <c r="BI47" t="n">
-        <v>1.86</v>
+        <v>1.48</v>
       </c>
       <c r="BJ47" t="n">
-        <v>1.84</v>
+        <v>2.47</v>
       </c>
       <c r="BK47" t="n">
-        <v>2.42</v>
+        <v>1.83</v>
       </c>
       <c r="BL47" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="BM47" t="n">
-        <v>3.22</v>
+        <v>2.05</v>
       </c>
       <c r="BN47" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="BO47" t="n">
-        <v>4.3</v>
+        <v>2.84</v>
       </c>
       <c r="BP47" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="48">
@@ -10807,7 +10807,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>8227210</v>
+        <v>8227366</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -10827,113 +10827,113 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N48" t="n">
         <v>3</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>['66']</t>
+          <t>['9', '90+7']</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>['74', '89']</t>
+          <t>['19']</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>3.17</v>
+        <v>2.3</v>
       </c>
       <c r="R48" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="S48" t="n">
-        <v>3.94</v>
+        <v>6.05</v>
       </c>
       <c r="T48" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="U48" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="V48" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="W48" t="n">
         <v>1.3</v>
       </c>
       <c r="X48" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y48" t="n">
         <v>1.05</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.27</v>
+        <v>1.65</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.72</v>
+        <v>5.05</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AD48" t="n">
-        <v>6.95</v>
+        <v>6.6</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AJ48" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AM48" t="n">
-        <v>1.6</v>
+        <v>1.97</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AO48" t="n">
         <v>0.5</v>
@@ -10942,16 +10942,16 @@
         <v>0.92</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="AR48" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.44</v>
       </c>
       <c r="AS48" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="AT48" t="n">
-        <v>1.72</v>
+        <v>2.23</v>
       </c>
       <c r="AU48" t="n">
         <v>6</v>
@@ -10960,64 +10960,64 @@
         <v>3</v>
       </c>
       <c r="AW48" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA48" t="n">
         <v>7</v>
       </c>
-      <c r="AY48" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA48" t="n">
-        <v>3</v>
-      </c>
       <c r="BB48" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BC48" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD48" t="n">
-        <v>1.7</v>
+        <v>1.31</v>
       </c>
       <c r="BE48" t="n">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="BF48" t="n">
-        <v>2.38</v>
+        <v>4.33</v>
       </c>
       <c r="BG48" t="n">
-        <v>1.26</v>
+        <v>1.54</v>
       </c>
       <c r="BH48" t="n">
-        <v>3.76</v>
+        <v>2.42</v>
       </c>
       <c r="BI48" t="n">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="BJ48" t="n">
-        <v>2.47</v>
+        <v>1.84</v>
       </c>
       <c r="BK48" t="n">
-        <v>1.83</v>
+        <v>2.42</v>
       </c>
       <c r="BL48" t="n">
-        <v>1.95</v>
+        <v>1.47</v>
       </c>
       <c r="BM48" t="n">
-        <v>2.05</v>
+        <v>3.22</v>
       </c>
       <c r="BN48" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="BO48" t="n">
-        <v>2.84</v>
+        <v>4.3</v>
       </c>
       <c r="BP48" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="49">
@@ -16911,7 +16911,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>8227379</v>
+        <v>8227212</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -16931,197 +16931,197 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="I76" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L76" t="n">
+        <v>1</v>
+      </c>
+      <c r="M76" t="n">
+        <v>2</v>
+      </c>
+      <c r="N76" t="n">
         <v>3</v>
       </c>
-      <c r="J76" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" t="n">
-        <v>3</v>
-      </c>
-      <c r="L76" t="n">
-        <v>5</v>
-      </c>
-      <c r="M76" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" t="n">
-        <v>5</v>
-      </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>['9', '22', '45+6', '50', '90+3']</t>
+          <t>['28']</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['50', '71']</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>1.56</v>
+        <v>3.16</v>
       </c>
       <c r="R76" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="S76" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U76" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V76" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="W76" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X76" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF76" t="n">
         <v>2.9</v>
       </c>
-      <c r="S76" t="n">
-        <v>9</v>
-      </c>
-      <c r="T76" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="U76" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="V76" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="W76" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="X76" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z76" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AA76" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AB76" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC76" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD76" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE76" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF76" t="n">
-        <v>6</v>
-      </c>
       <c r="AG76" t="n">
-        <v>1.42</v>
+        <v>2.2</v>
       </c>
       <c r="AH76" t="n">
-        <v>2.65</v>
+        <v>1.68</v>
       </c>
       <c r="AI76" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AJ76" t="n">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="AK76" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AL76" t="n">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="AM76" t="n">
-        <v>4.75</v>
+        <v>1.49</v>
       </c>
       <c r="AN76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO76" t="n">
-        <v>1.33</v>
+        <v>0.75</v>
       </c>
       <c r="AP76" t="n">
-        <v>2.33</v>
+        <v>1.08</v>
       </c>
       <c r="AQ76" t="n">
         <v>0.92</v>
       </c>
       <c r="AR76" t="n">
-        <v>2.18</v>
+        <v>1.36</v>
       </c>
       <c r="AS76" t="n">
-        <v>0.88</v>
+        <v>1.1</v>
       </c>
       <c r="AT76" t="n">
-        <v>3.06</v>
+        <v>2.46</v>
       </c>
       <c r="AU76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX76" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY76" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ76" t="n">
         <v>8</v>
       </c>
-      <c r="AV76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW76" t="n">
+      <c r="BA76" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB76" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC76" t="n">
         <v>9</v>
       </c>
-      <c r="AX76" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY76" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ76" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA76" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB76" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC76" t="n">
-        <v>10</v>
-      </c>
       <c r="BD76" t="n">
-        <v>1.09</v>
+        <v>1.78</v>
       </c>
       <c r="BE76" t="n">
-        <v>10</v>
+        <v>6.75</v>
       </c>
       <c r="BF76" t="n">
-        <v>9</v>
+        <v>2.75</v>
       </c>
       <c r="BG76" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="BH76" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="BI76" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="BJ76" t="n">
-        <v>2.41</v>
+        <v>2.19</v>
       </c>
       <c r="BK76" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="BL76" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="BM76" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="BN76" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="BO76" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="BP76" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="77">
@@ -17129,7 +17129,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>8227212</v>
+        <v>8227379</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -17149,197 +17149,197 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L77" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>['28']</t>
+          <t>['9', '22', '45+6', '50', '90+3']</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>['50', '71']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>3.16</v>
+        <v>1.56</v>
       </c>
       <c r="R77" t="n">
-        <v>1.98</v>
+        <v>2.9</v>
       </c>
       <c r="S77" t="n">
-        <v>3.35</v>
+        <v>9</v>
       </c>
       <c r="T77" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="U77" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="V77" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="W77" t="n">
-        <v>1.36</v>
+        <v>1.79</v>
       </c>
       <c r="X77" t="n">
-        <v>8.300000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="Z77" t="n">
-        <v>2.6</v>
+        <v>1.16</v>
       </c>
       <c r="AA77" t="n">
-        <v>3.2</v>
+        <v>7.9</v>
       </c>
       <c r="AB77" t="n">
-        <v>2.8</v>
+        <v>15</v>
       </c>
       <c r="AC77" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AD77" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AF77" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="AG77" t="n">
-        <v>2.2</v>
+        <v>1.42</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.68</v>
+        <v>2.65</v>
       </c>
       <c r="AI77" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AJ77" t="n">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="AK77" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO77" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL77" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AM77" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AN77" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO77" t="n">
-        <v>0.75</v>
-      </c>
       <c r="AP77" t="n">
-        <v>1.08</v>
+        <v>2.33</v>
       </c>
       <c r="AQ77" t="n">
         <v>0.92</v>
       </c>
       <c r="AR77" t="n">
-        <v>1.36</v>
+        <v>2.18</v>
       </c>
       <c r="AS77" t="n">
-        <v>1.1</v>
+        <v>0.88</v>
       </c>
       <c r="AT77" t="n">
-        <v>2.46</v>
+        <v>3.06</v>
       </c>
       <c r="AU77" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AV77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW77" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AX77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY77" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ77" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BA77" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BB77" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BC77" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD77" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BE77" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF77" t="n">
         <v>9</v>
       </c>
-      <c r="BD77" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BE77" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="BF77" t="n">
-        <v>2.75</v>
-      </c>
       <c r="BG77" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="BH77" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BI77" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="BJ77" t="n">
-        <v>2.19</v>
+        <v>2.41</v>
       </c>
       <c r="BK77" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="BL77" t="n">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="BM77" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="BN77" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="BO77" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="BP77" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="78">
@@ -17347,7 +17347,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>8227215</v>
+        <v>8227380</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -17367,197 +17367,197 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K78" t="n">
         <v>1</v>
       </c>
       <c r="L78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N78" t="n">
         <v>2</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>['41', '90+8']</t>
+          <t>['60']</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="R78" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S78" t="n">
-        <v>5.11</v>
+        <v>3.65</v>
       </c>
       <c r="T78" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="U78" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="V78" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="W78" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="X78" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="Y78" t="n">
         <v>1.08</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.85</v>
+        <v>2.36</v>
       </c>
       <c r="AA78" t="n">
-        <v>3</v>
+        <v>3.32</v>
       </c>
       <c r="AB78" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="AC78" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AD78" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AF78" t="n">
-        <v>3.29</v>
+        <v>3.1</v>
       </c>
       <c r="AG78" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AI78" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AJ78" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AK78" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AL78" t="n">
         <v>1.3</v>
       </c>
       <c r="AM78" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AN78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AQ78" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT78" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU78" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV78" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW78" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY78" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB78" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC78" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD78" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BE78" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF78" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BG78" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH78" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BI78" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BJ78" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BK78" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BL78" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM78" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BN78" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BO78" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="BP78" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AO78" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AP78" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AQ78" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="AR78" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AS78" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AT78" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AU78" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV78" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW78" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX78" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY78" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ78" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA78" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB78" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC78" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD78" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BE78" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="BF78" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BG78" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BH78" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI78" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BJ78" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BK78" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BL78" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BM78" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BN78" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BO78" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="BP78" t="n">
-        <v>1.3</v>
       </c>
     </row>
     <row r="79">
@@ -17565,7 +17565,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>8227380</v>
+        <v>8227215</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -17585,197 +17585,197 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
         <v>1</v>
       </c>
       <c r="L79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
         <v>2</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>['60']</t>
+          <t>['41', '90+8']</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>['37']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="R79" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="S79" t="n">
-        <v>3.65</v>
+        <v>5.11</v>
       </c>
       <c r="T79" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="U79" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="V79" t="n">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="W79" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="X79" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="Y79" t="n">
         <v>1.08</v>
       </c>
       <c r="Z79" t="n">
-        <v>2.36</v>
+        <v>1.85</v>
       </c>
       <c r="AA79" t="n">
-        <v>3.32</v>
+        <v>3</v>
       </c>
       <c r="AB79" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="AC79" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AD79" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AF79" t="n">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="AG79" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH79" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ79" t="n">
         <v>1.79</v>
       </c>
-      <c r="AI79" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AJ79" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AK79" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AL79" t="n">
         <v>1.3</v>
       </c>
       <c r="AM79" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AN79" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AO79" t="n">
-        <v>1.75</v>
+        <v>0.75</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AQ79" t="n">
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
       <c r="AR79" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="AS79" t="n">
-        <v>1.12</v>
+        <v>1.42</v>
       </c>
       <c r="AT79" t="n">
-        <v>2.38</v>
+        <v>2.87</v>
       </c>
       <c r="AU79" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB79" t="n">
         <v>4</v>
       </c>
-      <c r="AV79" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW79" t="n">
+      <c r="BC79" t="n">
         <v>9</v>
       </c>
-      <c r="AX79" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY79" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ79" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA79" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB79" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC79" t="n">
-        <v>11</v>
-      </c>
       <c r="BD79" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="BE79" t="n">
-        <v>6.75</v>
+        <v>6.7</v>
       </c>
       <c r="BF79" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="BG79" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="BH79" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="BI79" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="BJ79" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="BK79" t="n">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="BL79" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="BM79" t="n">
-        <v>2.41</v>
+        <v>2.05</v>
       </c>
       <c r="BN79" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="BO79" t="n">
-        <v>3.07</v>
+        <v>2.97</v>
       </c>
       <c r="BP79" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="80">
@@ -30645,7 +30645,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="n">
-        <v>8227282</v>
+        <v>8227397</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -30665,197 +30665,197 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R139" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S139" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="T139" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U139" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="V139" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W139" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X139" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW139" t="n">
         <v>3</v>
       </c>
-      <c r="L139" t="n">
-        <v>2</v>
-      </c>
-      <c r="M139" t="n">
-        <v>2</v>
-      </c>
-      <c r="N139" t="n">
-        <v>4</v>
-      </c>
-      <c r="O139" t="inlineStr">
-        <is>
-          <t>['8', '12']</t>
-        </is>
-      </c>
-      <c r="P139" t="inlineStr">
-        <is>
-          <t>['41', '48']</t>
-        </is>
-      </c>
-      <c r="Q139" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R139" t="n">
-        <v>2</v>
-      </c>
-      <c r="S139" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T139" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U139" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="V139" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="W139" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X139" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Y139" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z139" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA139" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB139" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC139" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD139" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AE139" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF139" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AG139" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AH139" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AI139" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AJ139" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AK139" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AL139" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AM139" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN139" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO139" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AP139" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ139" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR139" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AS139" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AT139" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AU139" t="n">
+      <c r="AX139" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY139" t="n">
         <v>5</v>
       </c>
-      <c r="AV139" t="n">
+      <c r="AZ139" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC139" t="n">
         <v>5</v>
       </c>
-      <c r="AW139" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX139" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY139" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ139" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA139" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB139" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC139" t="n">
-        <v>12</v>
-      </c>
       <c r="BD139" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="BE139" t="n">
         <v>7.5</v>
       </c>
       <c r="BF139" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BG139" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="BH139" t="n">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="BI139" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="BJ139" t="n">
-        <v>2.09</v>
+        <v>2.23</v>
       </c>
       <c r="BK139" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="BL139" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="BM139" t="n">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="BN139" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="BO139" t="n">
-        <v>3.6</v>
+        <v>3.31</v>
       </c>
       <c r="BP139" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="140">
@@ -30863,7 +30863,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="n">
-        <v>8227397</v>
+        <v>8227282</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -30883,197 +30883,197 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K140" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8', '12']</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41', '48']</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="R140" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S140" t="n">
-        <v>3.46</v>
+        <v>2.53</v>
       </c>
       <c r="T140" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="U140" t="n">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="V140" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="W140" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X140" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA140" t="n">
         <v>3.3</v>
       </c>
-      <c r="W140" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X140" t="n">
+      <c r="AB140" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB140" t="n">
         <v>8</v>
       </c>
-      <c r="Y140" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Z140" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA140" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB140" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC140" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD140" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE140" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF140" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AG140" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AH140" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI140" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ140" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AK140" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AL140" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AM140" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN140" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AO140" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AP140" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ140" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="AR140" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="AS140" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AT140" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AU140" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV140" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW140" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX140" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY140" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ140" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA140" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB140" t="n">
-        <v>3</v>
-      </c>
       <c r="BC140" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="BD140" t="n">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="BE140" t="n">
         <v>7.5</v>
       </c>
       <c r="BF140" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BL140" t="n">
         <v>1.67</v>
       </c>
-      <c r="BG140" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BH140" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BI140" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BJ140" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BK140" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BL140" t="n">
-        <v>1.76</v>
-      </c>
       <c r="BM140" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="BN140" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="BO140" t="n">
-        <v>3.31</v>
+        <v>3.6</v>
       </c>
       <c r="BP140" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="141">
@@ -32389,7 +32389,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="n">
-        <v>8227401</v>
+        <v>8227341</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -32409,197 +32409,197 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
         <v>1</v>
       </c>
       <c r="K147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L147" t="n">
         <v>3</v>
       </c>
       <c r="M147" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N147" t="n">
+        <v>6</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>['16', '69', '73']</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>['12', '51', '64']</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>6</v>
+      </c>
+      <c r="R147" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S147" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T147" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U147" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V147" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="W147" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X147" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK147" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AQ147" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AR147" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS147" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT147" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AU147" t="n">
         <v>4</v>
       </c>
-      <c r="O147" t="inlineStr">
-        <is>
-          <t>['34', '45+1', '80']</t>
-        </is>
-      </c>
-      <c r="P147" t="inlineStr">
-        <is>
-          <t>['45+3']</t>
-        </is>
-      </c>
-      <c r="Q147" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="R147" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="S147" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="T147" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U147" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="V147" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="W147" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="X147" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Y147" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z147" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AA147" t="n">
+      <c r="AV147" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW147" t="n">
         <v>7</v>
       </c>
-      <c r="AB147" t="n">
-        <v>13.47</v>
-      </c>
-      <c r="AC147" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD147" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE147" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF147" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AG147" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AH147" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AI147" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AJ147" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AK147" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AL147" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AM147" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AN147" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO147" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AP147" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AQ147" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AR147" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AS147" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AT147" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="AU147" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV147" t="n">
+      <c r="AX147" t="n">
         <v>4</v>
       </c>
-      <c r="AW147" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX147" t="n">
+      <c r="AY147" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ147" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA147" t="n">
         <v>5</v>
       </c>
-      <c r="AY147" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ147" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA147" t="n">
+      <c r="BB147" t="n">
         <v>7</v>
       </c>
-      <c r="BB147" t="n">
-        <v>3</v>
-      </c>
       <c r="BC147" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BD147" t="n">
-        <v>1.11</v>
+        <v>5.5</v>
       </c>
       <c r="BE147" t="n">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="BF147" t="n">
-        <v>7.8</v>
+        <v>1.23</v>
       </c>
       <c r="BG147" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BH147" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BI147" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BJ147" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BK147" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BL147" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BM147" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BN147" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BO147" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="BP147" t="n">
         <v>1.23</v>
-      </c>
-      <c r="BH147" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="BI147" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BJ147" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BK147" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BL147" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BM147" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BN147" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BO147" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BP147" t="n">
-        <v>1.38</v>
       </c>
     </row>
     <row r="148">
@@ -32607,7 +32607,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="n">
-        <v>8227341</v>
+        <v>8227401</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -32627,197 +32627,197 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J148" t="n">
         <v>1</v>
       </c>
       <c r="K148" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L148" t="n">
         <v>3</v>
       </c>
       <c r="M148" t="n">
+        <v>1</v>
+      </c>
+      <c r="N148" t="n">
+        <v>4</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>['34', '45+1', '80']</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>['45+3']</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R148" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="S148" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="T148" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U148" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V148" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="W148" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X148" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>13.47</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AI148" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AJ148" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AK148" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AL148" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AM148" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AN148" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO148" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AP148" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ148" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR148" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS148" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AT148" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AU148" t="n">
         <v>3</v>
       </c>
-      <c r="N148" t="n">
-        <v>6</v>
-      </c>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>['16', '69', '73']</t>
-        </is>
-      </c>
-      <c r="P148" t="inlineStr">
-        <is>
-          <t>['12', '51', '64']</t>
-        </is>
-      </c>
-      <c r="Q148" t="n">
-        <v>6</v>
-      </c>
-      <c r="R148" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="S148" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T148" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U148" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V148" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="W148" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X148" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Y148" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z148" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA148" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB148" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC148" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD148" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE148" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF148" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AG148" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH148" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AI148" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AJ148" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AK148" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AL148" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AM148" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AN148" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AO148" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AP148" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AQ148" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AR148" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AS148" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AT148" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="AU148" t="n">
+      <c r="AV148" t="n">
         <v>4</v>
       </c>
-      <c r="AV148" t="n">
-        <v>6</v>
-      </c>
       <c r="AW148" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX148" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY148" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ148" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA148" t="n">
         <v>7</v>
       </c>
-      <c r="AX148" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY148" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ148" t="n">
+      <c r="BB148" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC148" t="n">
         <v>10</v>
       </c>
-      <c r="BA148" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB148" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC148" t="n">
-        <v>12</v>
-      </c>
       <c r="BD148" t="n">
-        <v>5.5</v>
+        <v>1.11</v>
       </c>
       <c r="BE148" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="BF148" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG148" t="n">
         <v>1.23</v>
       </c>
-      <c r="BG148" t="n">
-        <v>1.42</v>
-      </c>
       <c r="BH148" t="n">
-        <v>2.61</v>
+        <v>3.58</v>
       </c>
       <c r="BI148" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="BJ148" t="n">
-        <v>2.04</v>
+        <v>2.56</v>
       </c>
       <c r="BK148" t="n">
-        <v>2.52</v>
+        <v>1.77</v>
       </c>
       <c r="BL148" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="BM148" t="n">
-        <v>2.78</v>
+        <v>2.26</v>
       </c>
       <c r="BN148" t="n">
-        <v>1.39</v>
+        <v>1.59</v>
       </c>
       <c r="BO148" t="n">
-        <v>3.74</v>
+        <v>2.8</v>
       </c>
       <c r="BP148" t="n">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="149">
@@ -34569,7 +34569,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="n">
-        <v>8227289</v>
+        <v>8227277</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -34589,197 +34589,197 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="I157" t="n">
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M157" t="n">
         <v>1</v>
       </c>
       <c r="N157" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['60', '69']</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>['42']</t>
+          <t>['62']</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>3.53</v>
+        <v>3.15</v>
       </c>
       <c r="R157" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S157" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="T157" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="U157" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="V157" t="n">
-        <v>3.22</v>
+        <v>3.66</v>
       </c>
       <c r="W157" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="X157" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="Y157" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z157" t="n">
-        <v>2.7</v>
+        <v>2.39</v>
       </c>
       <c r="AA157" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AB157" t="n">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="AC157" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AD157" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE157" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="AF157" t="n">
-        <v>2.99</v>
+        <v>2.55</v>
       </c>
       <c r="AG157" t="n">
-        <v>2.3</v>
+        <v>2.73</v>
       </c>
       <c r="AH157" t="n">
-        <v>1.63</v>
+        <v>1.46</v>
       </c>
       <c r="AI157" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AJ157" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AK157" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL157" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AM157" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN157" t="n">
         <v>1.44</v>
       </c>
-      <c r="AN157" t="n">
-        <v>0.33</v>
-      </c>
       <c r="AO157" t="n">
-        <v>0.63</v>
+        <v>1.22</v>
       </c>
       <c r="AP157" t="n">
-        <v>0.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ157" t="n">
-        <v>0.92</v>
+        <v>1.15</v>
       </c>
       <c r="AR157" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AS157" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="AT157" t="n">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="AU157" t="n">
         <v>3</v>
       </c>
       <c r="AV157" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW157" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX157" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY157" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ157" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA157" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC157" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD157" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BE157" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF157" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BG157" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BH157" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BI157" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BJ157" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BK157" t="n">
         <v>3</v>
       </c>
-      <c r="AW157" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX157" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY157" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ157" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA157" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB157" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC157" t="n">
+      <c r="BL157" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BM157" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="BN157" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BO157" t="n">
         <v>5</v>
       </c>
-      <c r="BD157" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BE157" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF157" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BG157" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BH157" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BI157" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BJ157" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="BK157" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BL157" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BM157" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BN157" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BO157" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BP157" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="158">
@@ -34787,7 +34787,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="n">
-        <v>8227277</v>
+        <v>8227289</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -34807,197 +34807,197 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="I158" t="n">
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L158" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
         <v>1</v>
       </c>
       <c r="N158" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>['60', '69']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>['62']</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>3.15</v>
+        <v>3.53</v>
       </c>
       <c r="R158" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S158" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="T158" t="n">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="U158" t="n">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="V158" t="n">
-        <v>3.66</v>
+        <v>3.22</v>
       </c>
       <c r="W158" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="X158" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="Y158" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Z158" t="n">
-        <v>2.39</v>
+        <v>2.7</v>
       </c>
       <c r="AA158" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AB158" t="n">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="AC158" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AD158" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE158" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="AF158" t="n">
-        <v>2.55</v>
+        <v>2.99</v>
       </c>
       <c r="AG158" t="n">
-        <v>2.73</v>
+        <v>2.3</v>
       </c>
       <c r="AH158" t="n">
-        <v>1.46</v>
+        <v>1.63</v>
       </c>
       <c r="AI158" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AJ158" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AK158" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL158" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AM158" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AN158" t="n">
-        <v>1.44</v>
+        <v>0.33</v>
       </c>
       <c r="AO158" t="n">
-        <v>1.22</v>
+        <v>0.63</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.15</v>
+        <v>0.92</v>
       </c>
       <c r="AR158" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AS158" t="n">
-        <v>1.05</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT158" t="n">
-        <v>2.32</v>
+        <v>2.17</v>
       </c>
       <c r="AU158" t="n">
         <v>3</v>
       </c>
       <c r="AV158" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW158" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX158" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY158" t="n">
         <v>12</v>
       </c>
-      <c r="AX158" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY158" t="n">
-        <v>15</v>
-      </c>
       <c r="AZ158" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="BA158" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BB158" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BC158" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD158" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="BE158" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BF158" t="n">
-        <v>2.18</v>
+        <v>1.74</v>
       </c>
       <c r="BG158" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="BH158" t="n">
-        <v>2.34</v>
+        <v>2.82</v>
       </c>
       <c r="BI158" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="BJ158" t="n">
-        <v>1.82</v>
+        <v>2.11</v>
       </c>
       <c r="BK158" t="n">
-        <v>3</v>
+        <v>2.06</v>
       </c>
       <c r="BL158" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="BM158" t="n">
-        <v>3.24</v>
+        <v>2.68</v>
       </c>
       <c r="BN158" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="BO158" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="BP158" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="159">

--- a/Bases_de_Dados/FootyStats/Portugal Liga NOS_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Portugal Liga NOS_20252026.xlsx
@@ -47805,13 +47805,13 @@
         <v>8</v>
       </c>
       <c r="AX217" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY217" t="n">
         <v>13</v>
       </c>
       <c r="AZ217" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA217" t="n">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Portugal Liga NOS_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Portugal Liga NOS_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP217"/>
+  <dimension ref="A1:BP220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,7 +1350,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.67</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.75</v>
@@ -3530,7 +3530,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ15" t="n">
         <v>1.69</v>
@@ -4184,7 +4184,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ19" t="n">
         <v>0.91</v>
@@ -5489,7 +5489,7 @@
         <v>3</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.42</v>
@@ -5928,7 +5928,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR25" t="n">
         <v>1.21</v>
@@ -6582,7 +6582,7 @@
         <v>1</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR28" t="n">
         <v>0.86</v>
@@ -6800,7 +6800,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR29" t="n">
         <v>1.76</v>
@@ -7669,7 +7669,7 @@
         <v>3</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ33" t="n">
         <v>2.5</v>
@@ -8541,7 +8541,7 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ37" t="n">
         <v>0.92</v>
@@ -8980,7 +8980,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR39" t="n">
         <v>1.32</v>
@@ -9195,7 +9195,7 @@
         <v>1</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ40" t="n">
         <v>0.92</v>
@@ -9416,7 +9416,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR41" t="n">
         <v>2.12</v>
@@ -9631,7 +9631,7 @@
         <v>3</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ42" t="n">
         <v>2.5</v>
@@ -10724,7 +10724,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR47" t="n">
         <v>0.9399999999999999</v>
@@ -12901,7 +12901,7 @@
         <v>2</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ57" t="n">
         <v>0.92</v>
@@ -13340,7 +13340,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR59" t="n">
         <v>1.36</v>
@@ -13773,7 +13773,7 @@
         <v>1</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ61" t="n">
         <v>0.91</v>
@@ -13994,7 +13994,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR62" t="n">
         <v>1.71</v>
@@ -14209,7 +14209,7 @@
         <v>0.67</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ63" t="n">
         <v>0.92</v>
@@ -16607,7 +16607,7 @@
         <v>1.75</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ74" t="n">
         <v>1.42</v>
@@ -16828,7 +16828,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR75" t="n">
         <v>1.46</v>
@@ -17264,7 +17264,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ77" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR77" t="n">
         <v>2.18</v>
@@ -17482,7 +17482,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR78" t="n">
         <v>1.26</v>
@@ -17697,7 +17697,7 @@
         <v>0.75</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ79" t="n">
         <v>0.91</v>
@@ -18351,7 +18351,7 @@
         <v>3</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ82" t="n">
         <v>2.75</v>
@@ -20534,7 +20534,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR92" t="n">
         <v>1.3</v>
@@ -20749,7 +20749,7 @@
         <v>1.2</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ93" t="n">
         <v>0.92</v>
@@ -21406,7 +21406,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ96" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR96" t="n">
         <v>1.41</v>
@@ -21839,7 +21839,7 @@
         <v>3</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ98" t="n">
         <v>2.75</v>
@@ -22496,7 +22496,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ101" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR101" t="n">
         <v>1.36</v>
@@ -22711,7 +22711,7 @@
         <v>2.2</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ102" t="n">
         <v>1.33</v>
@@ -25109,7 +25109,7 @@
         <v>1.5</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ113" t="n">
         <v>1.69</v>
@@ -25548,7 +25548,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR115" t="n">
         <v>1.4</v>
@@ -25763,10 +25763,10 @@
         <v>1.5</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ116" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR116" t="n">
         <v>1.33</v>
@@ -26856,7 +26856,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR121" t="n">
         <v>2.22</v>
@@ -27071,7 +27071,7 @@
         <v>0.83</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ122" t="n">
         <v>0.92</v>
@@ -27289,7 +27289,7 @@
         <v>2.67</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ123" t="n">
         <v>2.5</v>
@@ -29036,7 +29036,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ131" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR131" t="n">
         <v>1.21</v>
@@ -29472,7 +29472,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ133" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR133" t="n">
         <v>1.38</v>
@@ -29687,7 +29687,7 @@
         <v>3</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ134" t="n">
         <v>2.75</v>
@@ -30341,7 +30341,7 @@
         <v>0.86</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ137" t="n">
         <v>0.92</v>
@@ -31652,7 +31652,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR143" t="n">
         <v>1.65</v>
@@ -32088,7 +32088,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR145" t="n">
         <v>1.37</v>
@@ -32306,7 +32306,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ146" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR146" t="n">
         <v>1.4</v>
@@ -33611,7 +33611,7 @@
         <v>1.71</v>
       </c>
       <c r="AP152" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ152" t="n">
         <v>1.33</v>
@@ -34047,7 +34047,7 @@
         <v>0.88</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ154" t="n">
         <v>0.92</v>
@@ -34486,7 +34486,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ156" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR156" t="n">
         <v>1.65</v>
@@ -34701,7 +34701,7 @@
         <v>1.22</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ157" t="n">
         <v>1.15</v>
@@ -34922,7 +34922,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ158" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR158" t="n">
         <v>1.23</v>
@@ -36230,7 +36230,7 @@
         <v>1</v>
       </c>
       <c r="AQ164" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR164" t="n">
         <v>0.91</v>
@@ -36445,7 +36445,7 @@
         <v>0.75</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ165" t="n">
         <v>0.67</v>
@@ -37535,7 +37535,7 @@
         <v>0.78</v>
       </c>
       <c r="AP170" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ170" t="n">
         <v>0.92</v>
@@ -38628,7 +38628,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ175" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR175" t="n">
         <v>1.04</v>
@@ -38843,7 +38843,7 @@
         <v>1</v>
       </c>
       <c r="AP176" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ176" t="n">
         <v>0.92</v>
@@ -39282,7 +39282,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ178" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR178" t="n">
         <v>2.31</v>
@@ -40151,7 +40151,7 @@
         <v>1.4</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ182" t="n">
         <v>1.42</v>
@@ -41677,10 +41677,10 @@
         <v>0.22</v>
       </c>
       <c r="AP189" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ189" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR189" t="n">
         <v>1.51</v>
@@ -42552,7 +42552,7 @@
         <v>1</v>
       </c>
       <c r="AQ193" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR193" t="n">
         <v>0.9</v>
@@ -44296,7 +44296,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ201" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR201" t="n">
         <v>1.24</v>
@@ -44511,7 +44511,7 @@
         <v>0.6</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ202" t="n">
         <v>0.67</v>
@@ -44729,7 +44729,7 @@
         <v>2.45</v>
       </c>
       <c r="AP203" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ203" t="n">
         <v>2.5</v>
@@ -44950,7 +44950,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ204" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR204" t="n">
         <v>2.05</v>
@@ -45819,7 +45819,7 @@
         <v>1</v>
       </c>
       <c r="AP208" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ208" t="n">
         <v>0.92</v>
@@ -46040,7 +46040,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ209" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR209" t="n">
         <v>1.6</v>
@@ -47860,6 +47860,660 @@
       </c>
       <c r="BP217" t="n">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="n">
+        <v>8227302</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="n">
+        <v>46087.71875</v>
+      </c>
+      <c r="F218" t="n">
+        <v>25</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>FC Arouca</t>
+        </is>
+      </c>
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" t="n">
+        <v>0</v>
+      </c>
+      <c r="L218" t="n">
+        <v>1</v>
+      </c>
+      <c r="M218" t="n">
+        <v>0</v>
+      </c>
+      <c r="N218" t="n">
+        <v>1</v>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>['82']</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q218" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R218" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="S218" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T218" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U218" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="V218" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="W218" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X218" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y218" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z218" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA218" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB218" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC218" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD218" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE218" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF218" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AG218" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH218" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AI218" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AJ218" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AK218" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM218" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AN218" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO218" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP218" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AQ218" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AR218" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS218" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AT218" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU218" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV218" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW218" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX218" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY218" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ218" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA218" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB218" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC218" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD218" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE218" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF218" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG218" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH218" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI218" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ218" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BK218" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BL218" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BM218" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BN218" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO218" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP218" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" t="n">
+        <v>8227308</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="n">
+        <v>46088.52083333334</v>
+      </c>
+      <c r="F219" t="n">
+        <v>25</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>AVS</t>
+        </is>
+      </c>
+      <c r="I219" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" t="n">
+        <v>0</v>
+      </c>
+      <c r="K219" t="n">
+        <v>0</v>
+      </c>
+      <c r="L219" t="n">
+        <v>0</v>
+      </c>
+      <c r="M219" t="n">
+        <v>0</v>
+      </c>
+      <c r="N219" t="n">
+        <v>0</v>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q219" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="R219" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="S219" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="T219" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U219" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V219" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W219" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X219" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="Y219" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z219" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA219" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB219" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC219" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD219" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE219" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF219" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AG219" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH219" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AI219" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ219" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AK219" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM219" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AN219" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO219" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AP219" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ219" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AR219" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AS219" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AT219" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AU219" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV219" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW219" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX219" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY219" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ219" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA219" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB219" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC219" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD219" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BE219" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF219" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG219" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH219" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BI219" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ219" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BK219" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BL219" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BM219" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BN219" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO219" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BP219" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="n">
+        <v>8227309</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="n">
+        <v>46088.52083333334</v>
+      </c>
+      <c r="F220" t="n">
+        <v>25</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Moreirense FC</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>CD Nacional</t>
+        </is>
+      </c>
+      <c r="I220" t="n">
+        <v>1</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" t="n">
+        <v>1</v>
+      </c>
+      <c r="L220" t="n">
+        <v>1</v>
+      </c>
+      <c r="M220" t="n">
+        <v>1</v>
+      </c>
+      <c r="N220" t="n">
+        <v>2</v>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>['45+7']</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>['67']</t>
+        </is>
+      </c>
+      <c r="Q220" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R220" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="S220" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="T220" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U220" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V220" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="W220" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X220" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z220" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA220" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB220" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AC220" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD220" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AE220" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF220" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AG220" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH220" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AI220" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ220" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AK220" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM220" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AN220" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO220" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AP220" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ220" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AR220" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AS220" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AT220" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AU220" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV220" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW220" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX220" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY220" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ220" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA220" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB220" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC220" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD220" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BE220" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BF220" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BG220" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH220" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI220" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BJ220" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BK220" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BL220" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM220" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BN220" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO220" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP220" t="n">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Portugal Liga NOS_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Portugal Liga NOS_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP220"/>
+  <dimension ref="A1:BP222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ7" t="n">
         <v>0.92</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ8" t="n">
         <v>0.92</v>
@@ -4838,7 +4838,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ20" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AR20" t="n">
         <v>1.4</v>
@@ -5925,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ25" t="n">
         <v>0.25</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ36" t="n">
         <v>0.67</v>
@@ -8977,7 +8977,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ39" t="n">
         <v>0.25</v>
@@ -9634,7 +9634,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ42" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AR42" t="n">
         <v>1.01</v>
@@ -10285,7 +10285,7 @@
         <v>2</v>
       </c>
       <c r="AP45" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ45" t="n">
         <v>1.42</v>
@@ -13555,10 +13555,10 @@
         <v>3</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ60" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AR60" t="n">
         <v>1.38</v>
@@ -13991,7 +13991,7 @@
         <v>1.33</v>
       </c>
       <c r="AP62" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ62" t="n">
         <v>0.85</v>
@@ -17479,7 +17479,7 @@
         <v>1.75</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ78" t="n">
         <v>0.85</v>
@@ -17918,7 +17918,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ80" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AR80" t="n">
         <v>1.7</v>
@@ -18133,7 +18133,7 @@
         <v>1.5</v>
       </c>
       <c r="AP81" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ81" t="n">
         <v>0.92</v>
@@ -20531,7 +20531,7 @@
         <v>1</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ92" t="n">
         <v>0.85</v>
@@ -21188,7 +21188,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ95" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AR95" t="n">
         <v>1.55</v>
@@ -22057,7 +22057,7 @@
         <v>1.2</v>
       </c>
       <c r="AP99" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ99" t="n">
         <v>1.15</v>
@@ -24458,7 +24458,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ110" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AR110" t="n">
         <v>2.16</v>
@@ -25327,7 +25327,7 @@
         <v>1</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.15</v>
@@ -27943,7 +27943,7 @@
         <v>0.83</v>
       </c>
       <c r="AP126" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ126" t="n">
         <v>0.67</v>
@@ -28379,7 +28379,7 @@
         <v>1.71</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ128" t="n">
         <v>1.69</v>
@@ -30126,7 +30126,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ136" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AR136" t="n">
         <v>1.32</v>
@@ -30559,7 +30559,7 @@
         <v>1</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ138" t="n">
         <v>0.75</v>
@@ -31213,7 +31213,7 @@
         <v>2.71</v>
       </c>
       <c r="AP141" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ141" t="n">
         <v>2.5</v>
@@ -31870,7 +31870,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ144" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AR144" t="n">
         <v>1.58</v>
@@ -36666,7 +36666,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ166" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AR166" t="n">
         <v>1.25</v>
@@ -36881,7 +36881,7 @@
         <v>1.25</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ167" t="n">
         <v>0.91</v>
@@ -37753,7 +37753,7 @@
         <v>0.88</v>
       </c>
       <c r="AP171" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ171" t="n">
         <v>0.75</v>
@@ -40587,7 +40587,7 @@
         <v>0.7</v>
       </c>
       <c r="AP184" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ184" t="n">
         <v>0.92</v>
@@ -41241,7 +41241,7 @@
         <v>1.1</v>
       </c>
       <c r="AP187" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ187" t="n">
         <v>0.92</v>
@@ -41898,7 +41898,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ190" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AR190" t="n">
         <v>1.67</v>
@@ -44732,7 +44732,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ203" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AR203" t="n">
         <v>1</v>
@@ -45165,7 +45165,7 @@
         <v>1</v>
       </c>
       <c r="AP205" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ205" t="n">
         <v>0.91</v>
@@ -45383,7 +45383,7 @@
         <v>1.55</v>
       </c>
       <c r="AP206" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ206" t="n">
         <v>1.42</v>
@@ -48514,6 +48514,442 @@
       </c>
       <c r="BP220" t="n">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" t="n">
+        <v>8227436</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="n">
+        <v>46088.625</v>
+      </c>
+      <c r="F221" t="n">
+        <v>25</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Sporting Braga</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Sporting CP</t>
+        </is>
+      </c>
+      <c r="I221" t="n">
+        <v>1</v>
+      </c>
+      <c r="J221" t="n">
+        <v>2</v>
+      </c>
+      <c r="K221" t="n">
+        <v>3</v>
+      </c>
+      <c r="L221" t="n">
+        <v>2</v>
+      </c>
+      <c r="M221" t="n">
+        <v>2</v>
+      </c>
+      <c r="N221" t="n">
+        <v>4</v>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>['34', '90+6']</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>['22', '45+2']</t>
+        </is>
+      </c>
+      <c r="Q221" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="R221" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S221" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="T221" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U221" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="V221" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="W221" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X221" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z221" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA221" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB221" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC221" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD221" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE221" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF221" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AG221" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH221" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI221" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AJ221" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AK221" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM221" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN221" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AO221" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP221" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ221" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AR221" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS221" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AT221" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AU221" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV221" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW221" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX221" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY221" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ221" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA221" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB221" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC221" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD221" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BE221" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF221" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BG221" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BH221" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BI221" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BJ221" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BK221" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BL221" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BM221" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BN221" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BO221" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="BP221" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" t="n">
+        <v>8227304</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="n">
+        <v>46088.72916666666</v>
+      </c>
+      <c r="F222" t="n">
+        <v>25</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>GD Estoril Praia</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Casa Pia</t>
+        </is>
+      </c>
+      <c r="I222" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" t="n">
+        <v>0</v>
+      </c>
+      <c r="L222" t="n">
+        <v>0</v>
+      </c>
+      <c r="M222" t="n">
+        <v>0</v>
+      </c>
+      <c r="N222" t="n">
+        <v>0</v>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q222" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="R222" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S222" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T222" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U222" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="V222" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W222" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X222" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z222" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA222" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB222" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AC222" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD222" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="AE222" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF222" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AG222" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH222" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AI222" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AJ222" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AK222" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM222" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AN222" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO222" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP222" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AQ222" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR222" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS222" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT222" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AU222" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV222" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW222" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX222" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY222" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ222" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA222" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB222" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC222" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD222" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BE222" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF222" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BG222" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH222" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="BI222" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BJ222" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK222" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BL222" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM222" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BN222" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BO222" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BP222" t="n">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>
